--- a/apps/name-masker/selftest/樣本_Zuvio合成資料.xlsx
+++ b/apps/name-masker/selftest/樣本_Zuvio合成資料.xlsx
@@ -586,7 +586,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>411354043</v>
+        <v>990054043</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>411354044</v>
+        <v>990054044</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>411354045</t>
+          <t>990054045</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -663,7 +663,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>411354046</v>
+        <v>990054046</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>411354047</v>
+        <v>990054047</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>411354048</v>
+        <v>990054048</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>411354043</v>
+        <v>990054043</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>411354044</v>
+        <v>990054044</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>411354046</v>
+        <v>990054046</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>411354043</v>
+        <v>990054043</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>411354045</t>
+          <t>990054045</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -947,7 +947,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>411354049</v>
+        <v>990054049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>411354049</v>
+        <v>990054049</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>411354043</v>
+        <v>990054043</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
